--- a/data/trans_orig/IP07C08-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP07C08-Habitat-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2007 (tasa de respuesta: 89,69%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2007 (tasa de respuesta: 89,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>13335</t>
+          <t>13159</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25288</t>
+          <t>25035</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>23,19%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>43,98%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15804</t>
+          <t>15544</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>27939</t>
+          <t>27702</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32203</t>
+          <t>32792</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49293</t>
+          <t>49825</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,29%</t>
+          <t>39,71%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26044</t>
+          <t>26459</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>38055</t>
+          <t>38618</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,29%</t>
+          <t>46,01%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>67,16%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>31241</t>
+          <t>31565</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>44644</t>
+          <t>44872</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,68%</t>
+          <t>66,02%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>61068</t>
+          <t>61152</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>79161</t>
+          <t>78934</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,67%</t>
+          <t>48,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>63,09%</t>
+          <t>62,91%</t>
         </is>
       </c>
     </row>
@@ -958,12 +958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3191</t>
+          <t>3221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>11507</t>
+          <t>11263</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -973,12 +973,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4027</t>
+          <t>3816</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>12219</t>
+          <t>11839</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1028,12 +1028,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8891</t>
+          <t>8712</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>19640</t>
+          <t>20641</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>7,09%</t>
+          <t>6,94%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>15,65%</t>
+          <t>16,45%</t>
         </is>
       </c>
     </row>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4856</t>
+          <t>4944</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>7,14%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,7 +1146,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4356</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29321</t>
+          <t>28854</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>44462</t>
+          <t>43808</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1429,12 +1429,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>29,76%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>45,13%</t>
+          <t>44,46%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1449,12 +1449,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>26068</t>
+          <t>26194</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>41196</t>
+          <t>40827</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1464,12 +1464,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>44,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1484,12 +1484,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>59423</t>
+          <t>59812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>80266</t>
+          <t>80366</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1499,12 +1499,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>31,17%</t>
+          <t>31,38%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,11%</t>
+          <t>42,16%</t>
         </is>
       </c>
     </row>
@@ -1527,12 +1527,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>37358</t>
+          <t>37523</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>52728</t>
+          <t>53832</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1542,12 +1542,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1562,12 +1562,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>36171</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>52025</t>
+          <t>51615</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1577,12 +1577,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>40,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>56,49%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1597,12 +1597,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>79581</t>
+          <t>79918</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>100117</t>
+          <t>99742</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1612,12 +1612,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>52,52%</t>
+          <t>52,32%</t>
         </is>
       </c>
     </row>
@@ -1640,12 +1640,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9986</t>
+          <t>10325</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>21231</t>
+          <t>21428</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>21,55%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1675,12 +1675,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8681</t>
+          <t>8589</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19179</t>
+          <t>19310</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1690,12 +1690,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,33%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>20,82%</t>
+          <t>20,97%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1710,12 +1710,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21690</t>
+          <t>20947</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37285</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1725,12 +1725,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>10,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,01%</t>
         </is>
       </c>
     </row>
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3283</t>
+          <t>3296</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1773,7 +1773,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,7 +1793,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2965</t>
+          <t>3260</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,7 +1808,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,7 +1828,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>3818</t>
+          <t>4347</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>2,28%</t>
         </is>
       </c>
     </row>
@@ -1871,7 +1871,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3316</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,77 +1886,77 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
+          <t>3,37%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>679</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>3719</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>4,04%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>679</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>1340</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>3402</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>0,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>4538</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>1340</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>4709</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,38%</t>
         </is>
       </c>
     </row>
@@ -2096,12 +2096,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24144</t>
+          <t>24735</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>36148</t>
+          <t>36095</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2111,12 +2111,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>44,45%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>64,95%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2131,12 +2131,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>22727</t>
+          <t>23040</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>35819</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2146,12 +2146,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>37,98%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>59,05%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2166,12 +2166,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>50180</t>
+          <t>51629</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>67685</t>
+          <t>67570</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2181,12 +2181,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,14%</t>
+          <t>44,39%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>58,19%</t>
+          <t>58,09%</t>
         </is>
       </c>
     </row>
@@ -2209,12 +2209,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15557</t>
+          <t>15753</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>27222</t>
+          <t>26642</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2224,12 +2224,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>28,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2244,12 +2244,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18347</t>
+          <t>18258</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>30690</t>
+          <t>30294</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2259,12 +2259,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2279,12 +2279,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36937</t>
+          <t>37369</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>53579</t>
+          <t>53727</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2294,12 +2294,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>31,76%</t>
+          <t>32,13%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>46,07%</t>
+          <t>46,19%</t>
         </is>
       </c>
     </row>
@@ -2322,12 +2322,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>5751</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2337,12 +2337,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,89%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2357,12 +2357,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>4313</t>
+          <t>4043</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12172</t>
+          <t>12107</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2372,12 +2372,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,07%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2392,12 +2392,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15743</t>
+          <t>15390</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2407,12 +2407,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>13,54%</t>
+          <t>13,23%</t>
         </is>
       </c>
     </row>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4422</t>
+          <t>3858</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2455,7 +2455,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>7,95%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2510,7 +2510,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>3832</t>
+          <t>4370</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2525,7 +2525,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,76%</t>
         </is>
       </c>
     </row>
@@ -2778,12 +2778,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>20549</t>
+          <t>20709</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>35100</t>
+          <t>35496</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2793,12 +2793,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>44,82%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2813,12 +2813,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>26466</t>
+          <t>26758</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>40961</t>
+          <t>41844</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2828,12 +2828,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>30,03%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>46,48%</t>
+          <t>47,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2848,12 +2848,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>51840</t>
+          <t>51017</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>71512</t>
+          <t>71792</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2863,12 +2863,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>42,97%</t>
+          <t>43,13%</t>
         </is>
       </c>
     </row>
@@ -2891,12 +2891,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>32646</t>
+          <t>32507</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47610</t>
+          <t>47642</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2906,12 +2906,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>41,69%</t>
+          <t>41,51%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>60,8%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>34788</t>
+          <t>34721</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>49883</t>
+          <t>50225</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2941,12 +2941,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>39,47%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>56,6%</t>
+          <t>56,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>72250</t>
+          <t>71153</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>93479</t>
+          <t>92680</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2976,12 +2976,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>43,41%</t>
+          <t>42,75%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>56,16%</t>
+          <t>55,68%</t>
         </is>
       </c>
     </row>
@@ -3004,12 +3004,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>4664</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>15288</t>
+          <t>14419</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3019,12 +3019,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>5,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3039,12 +3039,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5985</t>
+          <t>6074</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>15648</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3054,12 +3054,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3074,12 +3074,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>13783</t>
+          <t>12945</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>28221</t>
+          <t>27129</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3089,12 +3089,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,28%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3137,7 +3137,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3157,7 +3157,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>4254</t>
+          <t>4515</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3187,12 +3187,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>676</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6261</t>
+          <t>5931</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3202,12 +3202,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,56%</t>
         </is>
       </c>
     </row>
@@ -3270,7 +3270,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3975</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3285,7 +3285,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3305,7 +3305,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>4182</t>
+          <t>3520</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3320,7 +3320,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,11%</t>
         </is>
       </c>
     </row>
@@ -3460,12 +3460,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>100604</t>
+          <t>99120</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>126536</t>
+          <t>127464</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3475,12 +3475,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,69%</t>
+          <t>34,18%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>43,63%</t>
+          <t>43,95%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3495,12 +3495,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>105042</t>
+          <t>105372</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>132332</t>
+          <t>132408</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>34,01%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>42,87%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3530,12 +3530,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>211862</t>
+          <t>211575</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>249789</t>
+          <t>249427</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3545,12 +3545,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>41,71%</t>
+          <t>41,65%</t>
         </is>
       </c>
     </row>
@@ -3573,12 +3573,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>124980</t>
+          <t>125719</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>151718</t>
+          <t>154353</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3588,12 +3588,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>43,1%</t>
+          <t>43,35%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3608,12 +3608,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>134902</t>
+          <t>134809</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>161484</t>
+          <t>162628</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>43,68%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>52,28%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3643,12 +3643,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>268570</t>
+          <t>269841</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>306873</t>
+          <t>309473</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3658,12 +3658,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,85%</t>
+          <t>45,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,68%</t>
         </is>
       </c>
     </row>
@@ -3686,12 +3686,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>26146</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>42995</t>
+          <t>43464</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3701,12 +3701,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>9,02%</t>
+          <t>8,85%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,99%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3721,12 +3721,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>29544</t>
+          <t>29316</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>48170</t>
+          <t>47211</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3756,12 +3756,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>59487</t>
+          <t>59463</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>85149</t>
+          <t>84762</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>14,22%</t>
+          <t>14,15%</t>
         </is>
       </c>
     </row>
@@ -3799,12 +3799,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1273</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7376</t>
+          <t>7321</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3814,12 +3814,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3834,12 +3834,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>1163</t>
+          <t>1157</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>7129</t>
+          <t>7069</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3869,12 +3869,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>3168</t>
+          <t>3190</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>11912</t>
+          <t>11828</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3889,7 +3889,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -3917,7 +3917,7 @@
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>3727</t>
+          <t>3995</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3932,7 +3932,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3952,7 +3952,7 @@
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4920</t>
+          <t>4776</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3967,7 +3967,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3982,12 +3982,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>664</t>
+          <t>659</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>6116</t>
+          <t>5483</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -4179,7 +4179,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2012 (tasa de respuesta: 95,52%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2012 (tasa de respuesta: 95,52%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4374,12 +4374,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>24513</t>
+          <t>24305</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>37721</t>
+          <t>37600</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4389,12 +4389,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,16%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>60,77%</t>
+          <t>60,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>28364</t>
+          <t>28323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>42308</t>
+          <t>42197</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4424,12 +4424,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>39,41%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>58,78%</t>
+          <t>58,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4444,12 +4444,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>56700</t>
+          <t>57032</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>75741</t>
+          <t>75665</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4459,12 +4459,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,3%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,45%</t>
         </is>
       </c>
     </row>
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>19994</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>32130</t>
+          <t>32343</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,82%</t>
+          <t>32,21%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>52,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20272</t>
+          <t>20636</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33950</t>
+          <t>34182</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>28,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>47,17%</t>
+          <t>47,49%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43432</t>
+          <t>43413</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>62500</t>
+          <t>62184</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>46,63%</t>
+          <t>46,39%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2001</t>
+          <t>2004</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>9270</t>
+          <t>9030</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4615,12 +4615,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>14,93%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4008</t>
+          <t>3944</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>13079</t>
+          <t>12451</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>8085</t>
+          <t>7301</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>18948</t>
+          <t>18104</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,51%</t>
         </is>
       </c>
     </row>
@@ -4753,7 +4753,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>4417</t>
+          <t>3892</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>6,14%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4458</t>
+          <t>4460</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4831,7 +4831,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>3495</t>
+          <t>3509</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4846,7 +4846,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,63%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>3746</t>
+          <t>3638</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4881,7 +4881,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4901,7 +4901,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4742</t>
+          <t>5492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4916,7 +4916,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>4,1%</t>
         </is>
       </c>
     </row>
@@ -5056,12 +5056,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36540</t>
+          <t>36828</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>52752</t>
+          <t>52846</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -5071,12 +5071,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>37,35%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,92%</t>
+          <t>54,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -5091,12 +5091,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>30983</t>
+          <t>31224</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>46250</t>
+          <t>46395</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>32,56%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,6%</t>
+          <t>48,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -5126,12 +5126,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>72346</t>
+          <t>71289</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>93923</t>
+          <t>93841</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>37,48%</t>
+          <t>36,94%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>48,66%</t>
+          <t>48,62%</t>
         </is>
       </c>
     </row>
@@ -5169,12 +5169,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35624</t>
+          <t>35264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>51410</t>
+          <t>51634</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -5184,12 +5184,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>36,41%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,55%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>35128</t>
+          <t>35767</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>51654</t>
+          <t>51479</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>36,91%</t>
+          <t>37,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,28%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>75265</t>
+          <t>74996</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>96842</t>
+          <t>97748</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>38,86%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>50,18%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4135</t>
+          <t>4543</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>12954</t>
+          <t>13815</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6713</t>
+          <t>6920</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17415</t>
+          <t>17067</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>18,3%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>13433</t>
+          <t>13531</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27429</t>
+          <t>27136</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,96%</t>
+          <t>7,01%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>14,06%</t>
         </is>
       </c>
     </row>
@@ -5400,7 +5400,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>3695</t>
+          <t>3754</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>3,78%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5435,7 +5435,7 @@
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>3540</t>
+          <t>3117</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5450,7 +5450,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5470,7 +5470,7 @@
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>5537</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5485,7 +5485,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,87%</t>
         </is>
       </c>
     </row>
@@ -5513,7 +5513,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3648</t>
+          <t>3834</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5528,7 +5528,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5548,7 +5548,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>4165</t>
+          <t>4172</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>622</t>
+          <t>623</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5678</t>
+          <t>5516</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5598,7 +5598,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -5738,12 +5738,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>22415</t>
+          <t>22462</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>35418</t>
+          <t>35075</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5753,12 +5753,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>34,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>54,35%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5773,12 +5773,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31030</t>
+          <t>31170</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>44251</t>
+          <t>43839</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5788,12 +5788,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,92%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>64,06%</t>
+          <t>63,46%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5808,12 +5808,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>56052</t>
+          <t>57242</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>74501</t>
+          <t>75063</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5823,12 +5823,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>41,75%</t>
+          <t>42,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>55,91%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>22014</t>
+          <t>22180</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34563</t>
+          <t>34833</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,04%</t>
+          <t>53,45%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>13299</t>
+          <t>12993</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25168</t>
+          <t>24547</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>35,53%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>38829</t>
+          <t>38884</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55823</t>
+          <t>55415</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>28,92%</t>
+          <t>28,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>41,28%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2941</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10558</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7235</t>
+          <t>7152</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>16725</t>
+          <t>17061</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,35%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,7%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>11871</t>
+          <t>12142</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>23804</t>
+          <t>25062</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,73%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>603</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>8,59%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -6117,7 +6117,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3673</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -6132,7 +6132,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,32%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1284</t>
+          <t>1226</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7888</t>
+          <t>7486</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,58%</t>
         </is>
       </c>
     </row>
@@ -6420,12 +6420,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>29020</t>
+          <t>28320</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>43289</t>
+          <t>43665</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6435,12 +6435,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>33,85%</t>
+          <t>33,04%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>50,5%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6455,12 +6455,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>30316</t>
+          <t>29789</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>45931</t>
+          <t>45787</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6470,12 +6470,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>33,74%</t>
+          <t>33,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>51,12%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6490,12 +6490,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>63535</t>
+          <t>62860</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>84231</t>
+          <t>85888</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6505,12 +6505,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>35,8%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,97%</t>
+          <t>48,92%</t>
         </is>
       </c>
     </row>
@@ -6533,12 +6533,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>35034</t>
+          <t>35790</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>50358</t>
+          <t>51800</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6548,12 +6548,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>41,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>60,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6568,12 +6568,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>28679</t>
+          <t>29344</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>44473</t>
+          <t>45437</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6583,12 +6583,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,66%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>49,49%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6603,12 +6603,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>69633</t>
+          <t>69105</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>91001</t>
+          <t>92009</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6618,12 +6618,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>39,36%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>52,4%</t>
         </is>
       </c>
     </row>
@@ -6646,12 +6646,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1558</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>9732</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -6661,12 +6661,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -6681,12 +6681,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7626</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>19494</t>
+          <t>19433</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6696,12 +6696,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>8,45%</t>
+          <t>8,49%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,63%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6716,12 +6716,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>11090</t>
+          <t>11730</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>26042</t>
+          <t>25662</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6731,12 +6731,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,62%</t>
         </is>
       </c>
     </row>
@@ -6794,47 +6794,47 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
+          <t>611</t>
+        </is>
+      </c>
+      <c r="M25" s="2" t="inlineStr">
+        <is>
+          <t>5063</t>
+        </is>
+      </c>
+      <c r="N25" s="2" t="inlineStr">
+        <is>
+          <t>2,15%</t>
+        </is>
+      </c>
+      <c r="O25" s="2" t="inlineStr">
+        <is>
+          <t>0,68%</t>
+        </is>
+      </c>
+      <c r="P25" s="2" t="inlineStr">
+        <is>
+          <t>5,63%</t>
+        </is>
+      </c>
+      <c r="Q25" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>1936</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
+        <is>
           <t>613</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>5231</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>2,15%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
-        <is>
-          <t>0,68%</t>
-        </is>
-      </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>5,82%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>1936</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>616</t>
-        </is>
-      </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5266</t>
+          <t>5385</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,07%</t>
         </is>
       </c>
     </row>
@@ -6877,7 +6877,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>5302</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6892,7 +6892,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6912,7 +6912,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>3200</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6942,12 +6942,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>763</t>
+          <t>756</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>6227</t>
+          <t>6157</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6962,7 +6962,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -7102,12 +7102,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>126732</t>
+          <t>125399</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>154780</t>
+          <t>155208</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -7117,12 +7117,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>40,78%</t>
+          <t>40,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -7137,12 +7137,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>134506</t>
+          <t>134379</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>164330</t>
+          <t>163929</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -7152,12 +7152,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>50,4%</t>
+          <t>50,27%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -7172,12 +7172,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>269592</t>
+          <t>267706</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>310401</t>
+          <t>310286</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -7187,12 +7187,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>42,03%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>48,72%</t>
         </is>
       </c>
     </row>
@@ -7215,12 +7215,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>125334</t>
+          <t>126044</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>154976</t>
+          <t>156359</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -7230,12 +7230,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>40,33%</t>
+          <t>40,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>49,86%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7250,12 +7250,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>110168</t>
+          <t>112337</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>140885</t>
+          <t>140199</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7265,12 +7265,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>33,79%</t>
+          <t>34,45%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>43,21%</t>
+          <t>43,0%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7285,12 +7285,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>245461</t>
+          <t>246755</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>285863</t>
+          <t>288349</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7300,12 +7300,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>38,54%</t>
+          <t>38,74%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,28%</t>
         </is>
       </c>
     </row>
@@ -7328,12 +7328,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16219</t>
+          <t>17035</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>30756</t>
+          <t>31349</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>10,09%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7363,12 +7363,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>33383</t>
+          <t>33139</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>53101</t>
+          <t>54614</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>10,24%</t>
+          <t>10,16%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>16,28%</t>
+          <t>16,75%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -7398,12 +7398,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>53985</t>
+          <t>55041</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>79786</t>
+          <t>79282</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,53%</t>
+          <t>12,45%</t>
         </is>
       </c>
     </row>
@@ -7441,12 +7441,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>1279</t>
+          <t>1304</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>7712</t>
+          <t>7363</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -7456,12 +7456,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>2,48%</t>
+          <t>2,37%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -7476,12 +7476,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2488</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>9965</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -7491,12 +7491,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -7516,7 +7516,7 @@
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>14267</t>
+          <t>14626</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -7531,7 +7531,7 @@
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,3%</t>
         </is>
       </c>
     </row>
@@ -7554,12 +7554,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>724</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>6662</t>
+          <t>6637</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -7589,12 +7589,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>727</t>
+          <t>775</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>6974</t>
+          <t>7036</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -7604,12 +7604,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -7624,12 +7624,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>2609</t>
+          <t>2185</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>10919</t>
+          <t>11035</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -7639,12 +7639,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,73%</t>
         </is>
       </c>
     </row>
@@ -7821,7 +7821,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores según frecuencia de haberse ayudado entre los amigos en 2016 (tasa de respuesta: 95,47%)</t>
+          <t>Menores según la frecuencia de haberse ayudado entre los/as amigos/as en 2016 (tasa de respuesta: 95,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8016,12 +8016,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>26844</t>
+          <t>27003</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>40533</t>
+          <t>41503</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8031,12 +8031,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,13%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>58,74%</t>
+          <t>60,15%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8051,12 +8051,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25920</t>
+          <t>25405</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39546</t>
+          <t>40771</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8066,12 +8066,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>36,49%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>57,39%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8086,12 +8086,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>55814</t>
+          <t>56205</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>76605</t>
+          <t>77409</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8101,12 +8101,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>54,7%</t>
+          <t>55,27%</t>
         </is>
       </c>
     </row>
@@ -8129,12 +8129,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>20820</t>
+          <t>20135</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>34208</t>
+          <t>34771</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8144,12 +8144,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,17%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>49,57%</t>
+          <t>50,39%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8164,12 +8164,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>19132</t>
+          <t>19429</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>33118</t>
+          <t>33203</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8179,12 +8179,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>26,93%</t>
+          <t>27,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8199,12 +8199,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>43554</t>
+          <t>42941</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>63904</t>
+          <t>62695</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8214,12 +8214,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>31,1%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>44,77%</t>
         </is>
       </c>
     </row>
@@ -8242,12 +8242,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3584</t>
+          <t>3741</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>12341</t>
+          <t>12963</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8257,12 +8257,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,42%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>18,79%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8277,12 +8277,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>6824</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>18413</t>
+          <t>18324</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8292,12 +8292,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8312,12 +8312,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>12900</t>
+          <t>12493</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>26230</t>
+          <t>27041</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8327,12 +8327,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>18,73%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>4084</t>
+          <t>3452</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8375,7 +8375,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>5,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3530</t>
+          <t>3604</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8410,7 +8410,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -8430,7 +8430,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4806</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,43%</t>
         </is>
       </c>
     </row>
@@ -8698,12 +8698,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>36423</t>
+          <t>36214</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51919</t>
+          <t>51934</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8713,12 +8713,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>35,41%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,78%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8733,12 +8733,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>48757</t>
+          <t>49547</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>64863</t>
+          <t>65461</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>47,48%</t>
+          <t>48,25%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>63,16%</t>
+          <t>63,74%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8768,12 +8768,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>90452</t>
+          <t>89900</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>112981</t>
+          <t>113129</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>44,13%</t>
+          <t>43,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>55,12%</t>
+          <t>55,19%</t>
         </is>
       </c>
     </row>
@@ -8811,12 +8811,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>38228</t>
+          <t>38099</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54093</t>
+          <t>54274</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8826,12 +8826,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,25%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>52,89%</t>
+          <t>53,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8846,12 +8846,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>28803</t>
+          <t>28650</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>44120</t>
+          <t>43702</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8861,12 +8861,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>27,9%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>42,96%</t>
+          <t>42,55%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8881,12 +8881,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>70669</t>
+          <t>70937</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>92762</t>
+          <t>92988</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>34,48%</t>
+          <t>34,61%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>45,26%</t>
+          <t>45,37%</t>
         </is>
       </c>
     </row>
@@ -8924,12 +8924,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>6310</t>
+          <t>6479</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16563</t>
+          <t>16366</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8939,12 +8939,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6,17%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>16,0%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8959,12 +8959,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>3204</t>
+          <t>2669</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10750</t>
+          <t>10653</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8974,12 +8974,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8994,12 +8994,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>10877</t>
+          <t>11043</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>22962</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9009,12 +9009,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,2%</t>
         </is>
       </c>
     </row>
@@ -9072,47 +9072,47 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>6560</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>6,39%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>2813</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
           <t>720</t>
         </is>
       </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7260</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>2,74%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>7,07%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>2813</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>718</t>
-        </is>
-      </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6742</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9127,7 +9127,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -9150,12 +9150,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>606</t>
+          <t>612</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>4994</t>
+          <t>5070</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9165,12 +9165,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9190,7 +9190,7 @@
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3029</t>
+          <t>3229</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9205,7 +9205,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>2,95%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>641</t>
+          <t>638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>5775</t>
+          <t>6020</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,82%</t>
+          <t>2,94%</t>
         </is>
       </c>
     </row>
@@ -9380,12 +9380,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>30109</t>
+          <t>29590</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>42866</t>
+          <t>43215</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9395,12 +9395,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>61,82%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9415,12 +9415,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>25597</t>
+          <t>25330</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>39771</t>
+          <t>39829</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9430,12 +9430,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>34,3%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,3%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9450,12 +9450,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>58998</t>
+          <t>59096</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>77458</t>
+          <t>79556</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9465,12 +9465,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,82%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>53,59%</t>
+          <t>55,04%</t>
         </is>
       </c>
     </row>
@@ -9493,12 +9493,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>21379</t>
+          <t>21416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>34073</t>
+          <t>34760</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9508,12 +9508,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>48,74%</t>
+          <t>49,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9528,12 +9528,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>25414</t>
+          <t>26017</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>39563</t>
+          <t>39994</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9543,12 +9543,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>34,06%</t>
+          <t>34,87%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9563,12 +9563,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>51434</t>
+          <t>51031</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>70842</t>
+          <t>70391</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9578,12 +9578,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>35,59%</t>
+          <t>35,31%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,7%</t>
         </is>
       </c>
     </row>
@@ -9606,12 +9606,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2473</t>
+          <t>2565</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10084</t>
+          <t>10294</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9621,12 +9621,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9641,12 +9641,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2683</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10702</t>
+          <t>10547</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9656,12 +9656,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>14,34%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9676,12 +9676,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>6855</t>
+          <t>6379</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17501</t>
+          <t>17425</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9691,12 +9691,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,41%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>12,06%</t>
         </is>
       </c>
     </row>
@@ -9754,12 +9754,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>890</t>
+          <t>772</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>7469</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9769,12 +9769,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,11%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9789,12 +9789,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>773</t>
+          <t>885</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>7308</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9804,12 +9804,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,54%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -9872,7 +9872,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>2787</t>
+          <t>2769</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9887,7 +9887,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>2879</t>
+          <t>2808</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9922,7 +9922,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>46100</t>
+          <t>46064</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>64625</t>
+          <t>63410</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>44,38%</t>
+          <t>44,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>62,21%</t>
+          <t>61,04%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>44407</t>
+          <t>44877</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>61427</t>
+          <t>62299</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>44,62%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>61,72%</t>
+          <t>62,59%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>96602</t>
+          <t>96442</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>121532</t>
+          <t>120203</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,49%</t>
+          <t>47,41%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>59,75%</t>
+          <t>59,09%</t>
         </is>
       </c>
     </row>
@@ -10175,12 +10175,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>27501</t>
+          <t>27739</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44663</t>
+          <t>44843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10190,12 +10190,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>26,7%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>42,99%</t>
+          <t>43,17%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -10210,12 +10210,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>25214</t>
+          <t>24975</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42003</t>
+          <t>40564</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10225,12 +10225,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,33%</t>
+          <t>25,09%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>42,2%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -10245,12 +10245,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>56494</t>
+          <t>57501</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>80065</t>
+          <t>79667</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -10260,12 +10260,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>27,77%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>39,36%</t>
+          <t>39,17%</t>
         </is>
       </c>
     </row>
@@ -10288,12 +10288,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6757</t>
+          <t>6382</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>17396</t>
+          <t>17951</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -10303,12 +10303,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,14%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -10323,12 +10323,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>7459</t>
+          <t>7708</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18865</t>
+          <t>18362</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -10338,12 +10338,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -10358,12 +10358,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>16984</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>32759</t>
+          <t>32839</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>8,35%</t>
+          <t>8,17%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>16,14%</t>
         </is>
       </c>
     </row>
@@ -10406,7 +10406,7 @@
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5238</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -10421,7 +10421,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -10441,7 +10441,7 @@
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2872</t>
+          <t>3218</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -10456,7 +10456,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10471,12 +10471,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>609</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5549</t>
+          <t>6259</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10486,12 +10486,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>3,08%</t>
         </is>
       </c>
     </row>
@@ -10554,7 +10554,7 @@
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>2611</t>
+          <t>3032</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10569,7 +10569,7 @@
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10589,7 +10589,7 @@
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>3661</t>
+          <t>2830</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10604,7 +10604,7 @@
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>153574</t>
+          <t>154255</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>185605</t>
+          <t>185656</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>44,51%</t>
+          <t>44,7%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>53,79%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>159736</t>
+          <t>160037</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>190683</t>
+          <t>191912</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,92%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>54,81%</t>
+          <t>55,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>324735</t>
+          <t>323165</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>367413</t>
+          <t>367519</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>46,86%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>53,02%</t>
+          <t>53,04%</t>
         </is>
       </c>
     </row>
@@ -10857,12 +10857,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>121985</t>
+          <t>121276</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>153216</t>
+          <t>151444</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10872,12 +10872,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>35,35%</t>
+          <t>35,15%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>44,4%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10892,12 +10892,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>114035</t>
+          <t>111644</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>145438</t>
+          <t>142613</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10907,12 +10907,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,09%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>41,81%</t>
+          <t>40,99%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10927,12 +10927,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>243733</t>
+          <t>244634</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>284899</t>
+          <t>285625</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10942,12 +10942,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>41,11%</t>
+          <t>41,22%</t>
         </is>
       </c>
     </row>
@@ -10970,12 +10970,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>25210</t>
+          <t>26417</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>45199</t>
+          <t>44878</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -10985,12 +10985,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,31%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -11005,12 +11005,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>27295</t>
+          <t>27140</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>45198</t>
+          <t>46065</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -11020,12 +11020,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>7,85%</t>
+          <t>7,8%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,24%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -11040,12 +11040,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>58251</t>
+          <t>58354</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>84399</t>
+          <t>85186</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -11055,12 +11055,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>12,29%</t>
         </is>
       </c>
     </row>
@@ -11083,12 +11083,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>682</t>
+          <t>683</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>6654</t>
+          <t>5670</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -11118,12 +11118,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>3492</t>
+          <t>3868</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>12763</t>
+          <t>13442</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -11133,12 +11133,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,86%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -11153,12 +11153,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>5027</t>
+          <t>5111</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>16296</t>
+          <t>16058</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -11168,12 +11168,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,32%</t>
         </is>
       </c>
     </row>
@@ -11196,12 +11196,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>611</t>
+          <t>614</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>5666</t>
+          <t>4962</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -11231,12 +11231,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>548</t>
+          <t>545</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>4839</t>
+          <t>5087</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -11251,7 +11251,7 @@
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>1269</t>
+          <t>1253</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>7596</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -11286,7 +11286,7 @@
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
